--- a/data/持倉月度追蹤.xlsx
+++ b/data/持倉月度追蹤.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,7 +488,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>✅B級+🔥強拐點</t>
+          <t>✅wang者級(配息防禦+小幅成長,非賠率爆發)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -498,36 +498,40 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+4% / +10% / -6% / +7% / +8% / +13%</t>
+          <t>+10% / -6% / +7% / +8% / +13% / +11%</t>
         </is>
       </c>
       <c r="F2" t="n">
         <v>36.45</v>
       </c>
       <c r="G2" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>持續觀察</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>真實賠率≈1.6(目標220下修後);成長股屬性已轉配息股,別期待翻倍</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2912</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>豆府</t>
+          <t>統一超</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>✅B級+🔥強拐點</t>
+          <t>零售內需(超商龍頭)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -537,14 +541,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+6% / -1% / +24% / +7% / +14% / +15%</t>
+          <t>+0% / +9% / +5% / +5% / +5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>53.04</v>
+        <v>34.58</v>
       </c>
       <c r="G3" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +560,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8462</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>柏文</t>
+          <t>神基</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>🔄循環+🔥強拐點</t>
+          <t>工業電腦/強固型(待補論點)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -576,14 +580,14 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+22% / +31% / +8% / +22% / +21% / +20%</t>
+          <t>+1% / -0% / -7% / +8% / +15% / +29%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>33.57</v>
+        <v>31.06</v>
       </c>
       <c r="G4" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -592,24 +596,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>盯負債比(現78%)別再升</t>
+          <t>⚠️現價已逼近停損100,跌破即出場</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>漢來美食</t>
+          <t>崇友</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>⭐A但拐點訊號雜(觀察區)</t>
+          <t>電梯/工程(待補論點)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -619,23 +623,191 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-3% / -17% / +62% / +20% / +25% / +11%</t>
+          <t>+10% / +29% / +9% / +4% / +1% / +12%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>48.89</v>
+        <v>33.53</v>
       </c>
       <c r="G5" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>持續觀察</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>毛利含季節性(Q1旺季);需扣季節後YoY續升才升評</t>
+      <c r="I5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5904</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>寶雅</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>⭐A級好公司⚠️現價估值頂峰(觀察非買進)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>✓ 正常</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>-2% / +23% / +21% / +17% / +19% / +8%</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>45.13</v>
+      </c>
+      <c r="G6" t="n">
+        <v>43</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>持續觀察</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>🔴現價殖利率4.25%&lt;27年均5.95%、PE位階99=歷史最貴;真買點490-540(殖利率回5.5%);現價賠率0.87&lt;1別追;拆股是行為利多非基本面;成長引擎已從展店量增轉效率提升(SSSG降5.6→2-3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>⭐A級+AI散熱供應鏈</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>✓ 正常</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>+36% / +2% / +22% / +15% / +15% / +19%</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>31.66</v>
+      </c>
+      <c r="G7" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>持續觀察</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EPS加速未兌現,賭 ROE 改善先行;2 季 EPS 仍未加速要重評。月營收動能已連2月降要盯</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>9918</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>欣天然</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>天然氣公用事業(防禦/高息)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>✓ 正常</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-9% / -16% / -1% / +2% / +11% / +1%</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>30.74</v>
+      </c>
+      <c r="G8" t="n">
+        <v>27</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>持續觀察</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>⚠️目標45/現價43.5,空間極小(賠率0.6);公用股本就低波,確認是否值得佔部位</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8016</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>矽創</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IC設計(驅動IC)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>✓ 正常</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>+27% / +10% / +29% / +37% / +40% / +27%</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="G9" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>持續觀察</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>⚠️現價305/停損300僅 1.6% 空間,停損過緊易被洗出,考慮放寬</t>
         </is>
       </c>
     </row>

--- a/data/持倉月度追蹤.xlsx
+++ b/data/持倉月度追蹤.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+10% / -6% / +7% / +8% / +13% / +11%</t>
+          <t>-6% / +7% / +8% / +13% / +11% / +10%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+0% / +9% / +5% / +5% / +5%</t>
+          <t>+9% / +5% / +5% / +5% / +6% / +8%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+1% / -0% / -7% / +8% / +15% / +29%</t>
+          <t>-0% / -7% / +8% / +15% / +29% / +16%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -618,12 +618,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>✓ 正常</t>
+          <t>⚠️ 警示</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+10% / +29% / +9% / +4% / +1% / +12%</t>
+          <t>+29% / +9% / +4% / +1% / +12% / -15%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>持續觀察</t>
+          <t>⚠️ 最新月 YoY -15.4% ≤ -8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-2% / +23% / +21% / +17% / +19% / +8%</t>
+          <t>+23% / +21% / +17% / +19% / +8% / +19%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+36% / +2% / +22% / +15% / +15% / +19%</t>
+          <t>+2% / +22% / +15% / +15% / +19% / +32%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-9% / -16% / -1% / +2% / +11% / +1%</t>
+          <t>-16% / -1% / +2% / +11% / +1% / +6%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+27% / +10% / +29% / +37% / +40% / +27%</t>
+          <t>+10% / +29% / +37% / +40% / +27% / +34%</t>
         </is>
       </c>
       <c r="F9" t="n">

--- a/data/持倉月度追蹤.xlsx
+++ b/data/持倉月度追蹤.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-6% / +7% / +8% / +13% / +11% / +10%</t>
+          <t>+7% / +8% / +13% / +11% / +10% / +9%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+9% / +5% / +5% / +5% / +6% / +8%</t>
+          <t>+5% / +5% / +5% / +6% / +8% / +5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -580,7 +580,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0% / -7% / +8% / +15% / +29% / +16%</t>
+          <t>-7% / +8% / +15% / +29% / +16% / +18%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -623,7 +623,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+29% / +9% / +4% / +1% / +12% / -15%</t>
+          <t>+9% / +4% / +1% / +12% / -15% / -12%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -634,7 +634,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>⚠️ 最新月 YoY -15.4% ≤ -8%</t>
+          <t>⚠️ 最新月 YoY -11.6% ≤ -8%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+23% / +21% / +17% / +19% / +8% / +19%</t>
+          <t>+21% / +17% / +19% / +8% / +19% / +10%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -705,7 +705,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+2% / +22% / +15% / +15% / +19% / +32%</t>
+          <t>+22% / +15% / +15% / +19% / +32% / +26%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-16% / -1% / +2% / +11% / +1% / +6%</t>
+          <t>-1% / +2% / +11% / +1% / +6% / +16%</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+10% / +29% / +37% / +40% / +27% / +34%</t>
+          <t>+29% / +37% / +40% / +27% / +34% / +24%</t>
         </is>
       </c>
       <c r="F9" t="n">
